--- a/Results/Summary Stats.xlsx
+++ b/Results/Summary Stats.xlsx
@@ -16,10 +16,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
-    <t>SGrowth_2023_2019</t>
-  </si>
-  <si>
-    <t>LSGrowth_2023_2019</t>
+    <t>LSGrowth_2023_2019_win</t>
   </si>
   <si>
     <t>Starting_INT</t>
@@ -31,10 +28,13 @@
     <t>Starting_Size_ln</t>
   </si>
   <si>
-    <t>Starting_Profit</t>
-  </si>
-  <si>
-    <t>HGX%</t>
+    <t>Starting_ROS</t>
+  </si>
+  <si>
+    <t>HGX_num</t>
+  </si>
+  <si>
+    <t>P/F_num</t>
   </si>
   <si>
     <t>count</t>
@@ -473,25 +473,25 @@
         <v>8</v>
       </c>
       <c r="B3">
-        <v>48.94737648153436</v>
+        <v>0.3155918540622472</v>
       </c>
       <c r="C3">
-        <v>0.2935806965605974</v>
+        <v>0.3113338928682742</v>
       </c>
       <c r="D3">
-        <v>31.13338928682742</v>
+        <v>0.4200568445732775</v>
       </c>
       <c r="E3">
-        <v>0.4200568445732775</v>
+        <v>13.47056692564208</v>
       </c>
       <c r="F3">
-        <v>13.47056692564208</v>
+        <v>0.03950992765804739</v>
       </c>
       <c r="G3">
-        <v>0.03950992765804739</v>
+        <v>0.403771491957848</v>
       </c>
       <c r="H3">
-        <v>-0.009812136347166621</v>
+        <v>0.4847476428175264</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -499,25 +499,25 @@
         <v>9</v>
       </c>
       <c r="B4">
-        <v>92.2230732451266</v>
+        <v>0.3481228834564474</v>
       </c>
       <c r="C4">
-        <v>0.5413950655413687</v>
+        <v>0.351766319087618</v>
       </c>
       <c r="D4">
-        <v>35.17663190876191</v>
+        <v>0.2482900782140482</v>
       </c>
       <c r="E4">
-        <v>0.2482900782140482</v>
+        <v>0.8453726038218823</v>
       </c>
       <c r="F4">
-        <v>0.8453726038218823</v>
+        <v>0.07592963679441075</v>
       </c>
       <c r="G4">
-        <v>0.07592963679441075</v>
+        <v>0.4907888245321261</v>
       </c>
       <c r="H4">
-        <v>0.162304729528329</v>
+        <v>0.4999059623985982</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -525,25 +525,25 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>-99.8852710128965</v>
+        <v>-0.6701799116473041</v>
       </c>
       <c r="C5">
-        <v>-6.770352751721602</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>-1.43996073261185</v>
       </c>
       <c r="E5">
-        <v>-1.43996073261185</v>
+        <v>12.17236590246427</v>
       </c>
       <c r="F5">
-        <v>12.17236590246427</v>
+        <v>-0.6982980223725119</v>
       </c>
       <c r="G5">
-        <v>-0.6982980223725119</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>-0.9965545290052217</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -551,25 +551,25 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>14.52204435477605</v>
+        <v>0.1355971422632631</v>
       </c>
       <c r="C6">
-        <v>0.1355971422632631</v>
+        <v>0.001299400835988426</v>
       </c>
       <c r="D6">
-        <v>0.1299400835988426</v>
+        <v>0.2529723413193963</v>
       </c>
       <c r="E6">
-        <v>0.2529723413193963</v>
+        <v>12.8424259011645</v>
       </c>
       <c r="F6">
-        <v>12.8424259011645</v>
+        <v>0.008283067495853256</v>
       </c>
       <c r="G6">
-        <v>0.008283067495853256</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>-0.01899421591852191</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -577,22 +577,22 @@
         <v>12</v>
       </c>
       <c r="B7">
-        <v>38.17163419627651</v>
+        <v>0.3233264524425223</v>
       </c>
       <c r="C7">
-        <v>0.3233264524425223</v>
+        <v>0.1403332244629682</v>
       </c>
       <c r="D7">
-        <v>14.03332244629682</v>
+        <v>0.4115027799527248</v>
       </c>
       <c r="E7">
-        <v>0.4115027799527248</v>
+        <v>13.22765989101407</v>
       </c>
       <c r="F7">
-        <v>13.22765989101407</v>
+        <v>0.02606610460031464</v>
       </c>
       <c r="G7">
-        <v>0.02606610460031464</v>
+        <v>0</v>
       </c>
       <c r="H7">
         <v>0</v>
@@ -603,25 +603,25 @@
         <v>13</v>
       </c>
       <c r="B8">
-        <v>65.61888515584661</v>
+        <v>0.504519090053293</v>
       </c>
       <c r="C8">
-        <v>0.504519090053293</v>
+        <v>0.6131606276349302</v>
       </c>
       <c r="D8">
-        <v>61.31606276349302</v>
+        <v>0.5918077795627114</v>
       </c>
       <c r="E8">
-        <v>0.5918077795627114</v>
+        <v>13.82922602091509</v>
       </c>
       <c r="F8">
-        <v>13.82922602091509</v>
+        <v>0.05807013692235607</v>
       </c>
       <c r="G8">
-        <v>0.05807013692235607</v>
+        <v>1</v>
       </c>
       <c r="H8">
-        <v>0.01991921880719105</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -629,25 +629,25 @@
         <v>14</v>
       </c>
       <c r="B9">
-        <v>2732.350803043111</v>
+        <v>1.085774545612381</v>
       </c>
       <c r="C9">
-        <v>3.343692132285168</v>
+        <v>1.000001044521693</v>
       </c>
       <c r="D9">
-        <v>100.0001044521693</v>
+        <v>0.9832084167935834</v>
       </c>
       <c r="E9">
-        <v>0.9832084167935834</v>
+        <v>17.83322147217127</v>
       </c>
       <c r="F9">
-        <v>17.83322147217127</v>
+        <v>0.9036493945910843</v>
       </c>
       <c r="G9">
-        <v>0.9036493945910843</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>0.9967764644841388</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
